--- a/exports/trend_1d/HCLTECH_full_report.xlsx
+++ b/exports/trend_1d/HCLTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42094</v>
+        <v>42095</v>
       </c>
       <c r="H2" t="n">
-        <v>490.2</v>
+        <v>470.4</v>
       </c>
       <c r="I2" t="n">
         <v>480.6341302183346</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" t="n">
-        <v>23.07</v>
+        <v>18.1</v>
       </c>
       <c r="L2" t="n">
         <v>2.56</v>
       </c>
       <c r="M2" t="n">
-        <v>1.33</v>
+        <v>3.41</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>4.04</v>
       </c>
       <c r="O2" t="n">
         <v>0.91</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42144</v>
+        <v>42145</v>
       </c>
       <c r="H3" t="n">
-        <v>480.05</v>
+        <v>485.1</v>
       </c>
       <c r="I3" t="n">
         <v>483.4293387362906</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.05</v>
+        <v>-3.13</v>
       </c>
       <c r="L3" t="n">
         <v>4.01</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42166</v>
+        <v>42167</v>
       </c>
       <c r="H4" t="n">
-        <v>457.4</v>
+        <v>448.15</v>
       </c>
       <c r="I4" t="n">
         <v>454.9929408602668</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.71</v>
+        <v>-7.62</v>
       </c>
       <c r="L4" t="n">
-        <v>7.11</v>
+        <v>9.02</v>
       </c>
       <c r="M4" t="n">
         <v>1.77</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>10.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42215</v>
+        <v>42216</v>
       </c>
       <c r="H5" t="n">
-        <v>478.95</v>
+        <v>499.1</v>
       </c>
       <c r="I5" t="n">
         <v>496.2100053583319</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.87</v>
+        <v>-11.37</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>12.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.37</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="O5" t="n">
         <v>-2.02</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42241</v>
+        <v>42242</v>
       </c>
       <c r="H6" t="n">
-        <v>457</v>
+        <v>451.2</v>
       </c>
       <c r="I6" t="n">
         <v>455.3620263523767</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.44</v>
+        <v>-9.6</v>
       </c>
       <c r="L6" t="n">
-        <v>10.85</v>
+        <v>11.44</v>
       </c>
       <c r="M6" t="n">
         <v>4.59</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.55</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H7" t="n">
-        <v>422.25</v>
+        <v>432.85</v>
       </c>
       <c r="I7" t="n">
         <v>432.3424860480561</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K7" t="n">
-        <v>6.42</v>
+        <v>4.07</v>
       </c>
       <c r="L7" t="n">
         <v>9.67</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>413.7</v>
+        <v>404</v>
       </c>
       <c r="I8" t="n">
         <v>404.0060452140045</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.42</v>
+        <v>-6.67</v>
       </c>
       <c r="L8" t="n">
-        <v>6.91</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>0.79</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42538</v>
+        <v>42541</v>
       </c>
       <c r="H9" t="n">
-        <v>376.8</v>
+        <v>385.3</v>
       </c>
       <c r="I9" t="n">
         <v>382.7268166692596</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K9" t="n">
-        <v>6.73</v>
+        <v>4.63</v>
       </c>
       <c r="L9" t="n">
         <v>7.22</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>6.77</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42548</v>
+        <v>42549</v>
       </c>
       <c r="H10" t="n">
-        <v>367.5</v>
+        <v>356.6</v>
       </c>
       <c r="I10" t="n">
         <v>363.9367169569371</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.62</v>
+        <v>-7.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.44</v>
+        <v>7.72</v>
       </c>
       <c r="M10" t="n">
         <v>3.36</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.51</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="H11" t="n">
-        <v>376.45</v>
+        <v>390.2</v>
       </c>
       <c r="I11" t="n">
         <v>382.427111430747</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.57</v>
+        <v>-9.42</v>
       </c>
       <c r="L11" t="n">
-        <v>6.41</v>
+        <v>10.91</v>
       </c>
       <c r="M11" t="n">
         <v>0.66</v>
       </c>
       <c r="N11" t="n">
-        <v>2.27</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
         <v>-2.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42601</v>
+        <v>42604</v>
       </c>
       <c r="H12" t="n">
-        <v>390.9</v>
+        <v>386.1</v>
       </c>
       <c r="I12" t="n">
         <v>387.1626338748543</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>0.18</v>
+        <v>-1.05</v>
       </c>
       <c r="L12" t="n">
         <v>3.58</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8.18</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42660</v>
+        <v>42661</v>
       </c>
       <c r="H13" t="n">
-        <v>404.2</v>
+        <v>417.4</v>
       </c>
       <c r="I13" t="n">
         <v>414.3494844135119</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.69</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.85</v>
+        <v>8.31</v>
       </c>
       <c r="M13" t="n">
         <v>0.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.49</v>
+        <v>3.27</v>
       </c>
       <c r="O13" t="n">
         <v>-1.23</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>8.35</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H14" t="n">
-        <v>395.4</v>
+        <v>387.15</v>
       </c>
       <c r="I14" t="n">
         <v>387.9544160583359</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.27</v>
+        <v>-7.25</v>
       </c>
       <c r="L14" t="n">
-        <v>5.65</v>
+        <v>7.61</v>
       </c>
       <c r="M14" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="N14" t="n">
         <v>2.54</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42717</v>
+        <v>42718</v>
       </c>
       <c r="H15" t="n">
-        <v>400.45</v>
+        <v>410.4</v>
       </c>
       <c r="I15" t="n">
         <v>408.6347726432131</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.44</v>
+        <v>-6.01</v>
       </c>
       <c r="L15" t="n">
         <v>6.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="H16" t="n">
-        <v>415.8</v>
+        <v>404.55</v>
       </c>
       <c r="I16" t="n">
         <v>411.8894810200009</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>1.32</v>
+        <v>-1.43</v>
       </c>
       <c r="L16" t="n">
         <v>5.14</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H17" t="n">
-        <v>428.7</v>
+        <v>432.45</v>
       </c>
       <c r="I17" t="n">
         <v>429.4233268399697</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.97</v>
+        <v>-6.9</v>
       </c>
       <c r="L17" t="n">
         <v>7.8</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42975</v>
+        <v>42976</v>
       </c>
       <c r="H18" t="n">
-        <v>433.8</v>
+        <v>426.25</v>
       </c>
       <c r="I18" t="n">
         <v>427.814413536067</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K18" t="n">
-        <v>0.31</v>
+        <v>-1.43</v>
       </c>
       <c r="L18" t="n">
         <v>4.17</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.27</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43013</v>
+        <v>43014</v>
       </c>
       <c r="H19" t="n">
-        <v>446.55</v>
+        <v>453.95</v>
       </c>
       <c r="I19" t="n">
         <v>452.1157922092838</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.76</v>
+        <v>-6.5</v>
       </c>
       <c r="L19" t="n">
-        <v>5.77</v>
+        <v>6.63</v>
       </c>
       <c r="M19" t="n">
         <v>0.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.49</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H20" t="n">
-        <v>453.5</v>
+        <v>434.5</v>
       </c>
       <c r="I20" t="n">
         <v>441.7571394985808</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1</v>
+        <v>-4.28</v>
       </c>
       <c r="L20" t="n">
-        <v>3.51</v>
+        <v>5.5</v>
       </c>
       <c r="M20" t="n">
         <v>2.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>4.19</v>
       </c>
       <c r="O20" t="n">
         <v>1.66</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.04</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H21" t="n">
-        <v>441.4</v>
+        <v>445.9</v>
       </c>
       <c r="I21" t="n">
         <v>443.8447436152686</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.59</v>
+        <v>-2.62</v>
       </c>
       <c r="L21" t="n">
         <v>4.72</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="H22" t="n">
-        <v>476.9</v>
+        <v>469.25</v>
       </c>
       <c r="I22" t="n">
         <v>470.3739467482869</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>6.95</v>
+        <v>5.24</v>
       </c>
       <c r="L22" t="n">
         <v>3.12</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43201</v>
+        <v>43202</v>
       </c>
       <c r="H23" t="n">
-        <v>483.65</v>
+        <v>505</v>
       </c>
       <c r="I23" t="n">
         <v>503.584653323624</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.07</v>
+        <v>-7.62</v>
       </c>
       <c r="L23" t="n">
-        <v>5.38</v>
+        <v>7.94</v>
       </c>
       <c r="M23" t="n">
         <v>1.22</v>
       </c>
       <c r="N23" t="n">
-        <v>3.91</v>
+        <v>4.41</v>
       </c>
       <c r="O23" t="n">
         <v>-1.6</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43222</v>
+        <v>43223</v>
       </c>
       <c r="H24" t="n">
-        <v>500.25</v>
+        <v>462.85</v>
       </c>
       <c r="I24" t="n">
         <v>492.8940651083636</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-8.35</v>
       </c>
       <c r="L24" t="n">
-        <v>4.23</v>
+        <v>8.91</v>
       </c>
       <c r="M24" t="n">
         <v>1.23</v>
       </c>
       <c r="N24" t="n">
-        <v>4.96</v>
+        <v>7.48</v>
       </c>
       <c r="O24" t="n">
         <v>4.41</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>17.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H25" t="n">
-        <v>480.75</v>
+        <v>489.75</v>
       </c>
       <c r="I25" t="n">
         <v>480.9537491887604</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.87</v>
+        <v>-5.81</v>
       </c>
       <c r="L25" t="n">
         <v>7.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3</v>
+        <v>3.48</v>
       </c>
       <c r="N25" t="n">
         <v>2.7</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.8</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H26" t="n">
-        <v>525.9</v>
+        <v>504.5</v>
       </c>
       <c r="I26" t="n">
         <v>524.1277836907886</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K26" t="n">
-        <v>7.38</v>
+        <v>3.01</v>
       </c>
       <c r="L26" t="n">
         <v>3.72</v>
       </c>
       <c r="M26" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>4.07</v>
       </c>
       <c r="O26" t="n">
         <v>1.87</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43494</v>
+        <v>43495</v>
       </c>
       <c r="H27" t="n">
-        <v>494.2</v>
+        <v>509.2</v>
       </c>
       <c r="I27" t="n">
         <v>495.2285128878672</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
-        <v>2.04</v>
+        <v>-0.93</v>
       </c>
       <c r="L27" t="n">
         <v>5.62</v>
       </c>
       <c r="M27" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="N27" t="n">
         <v>5.06</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.11</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H28" t="n">
-        <v>541.8</v>
+        <v>533.9</v>
       </c>
       <c r="I28" t="n">
         <v>540.2362952804837</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>4.85</v>
       </c>
       <c r="L28" t="n">
         <v>3.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H29" t="n">
-        <v>511.3</v>
+        <v>544.1</v>
       </c>
       <c r="I29" t="n">
         <v>535.1904343851091</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K29" t="n">
-        <v>4.23</v>
+        <v>-1.91</v>
       </c>
       <c r="L29" t="n">
         <v>4.79</v>
       </c>
       <c r="M29" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.22</v>
+        <v>6.42</v>
       </c>
       <c r="O29" t="n">
         <v>-1.46</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.63</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H30" t="n">
-        <v>524.55</v>
+        <v>516.45</v>
       </c>
       <c r="I30" t="n">
         <v>517.8343477069985</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.59</v>
+        <v>-5.08</v>
       </c>
       <c r="L30" t="n">
-        <v>5.53</v>
+        <v>6.54</v>
       </c>
       <c r="M30" t="n">
         <v>0.97</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H31" t="n">
-        <v>547.55</v>
+        <v>559.5</v>
       </c>
       <c r="I31" t="n">
         <v>559.1033723927752</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.02</v>
+        <v>-8.34</v>
       </c>
       <c r="L31" t="n">
-        <v>7.17</v>
+        <v>12.21</v>
       </c>
       <c r="M31" t="n">
-        <v>1.32</v>
+        <v>5.48</v>
       </c>
       <c r="N31" t="n">
         <v>3.8</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.2</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43810</v>
+        <v>43811</v>
       </c>
       <c r="H32" t="n">
-        <v>543.8</v>
+        <v>536.35</v>
       </c>
       <c r="I32" t="n">
         <v>542.2485938194494</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.81</v>
+        <v>-4.14</v>
       </c>
       <c r="L32" t="n">
-        <v>3.58</v>
+        <v>4.37</v>
       </c>
       <c r="M32" t="n">
         <v>0.55</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.9</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H33" t="n">
-        <v>571.95</v>
+        <v>573.55</v>
       </c>
       <c r="I33" t="n">
         <v>572.2207930876297</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.64</v>
+        <v>-6.94</v>
       </c>
       <c r="L33" t="n">
         <v>7.67</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="H34" t="n">
-        <v>583.6</v>
+        <v>573.05</v>
       </c>
       <c r="I34" t="n">
         <v>582.3797375939183</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
-        <v>1.75</v>
+        <v>-0.09</v>
       </c>
       <c r="L34" t="n">
-        <v>0.53</v>
+        <v>0.97</v>
       </c>
       <c r="M34" t="n">
         <v>1.39</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.35</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H35" t="n">
-        <v>491.75</v>
+        <v>543.55</v>
       </c>
       <c r="I35" t="n">
         <v>515.3298523306801</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>14.19</v>
+        <v>5.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.63</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>18.9</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44137</v>
+        <v>44138</v>
       </c>
       <c r="H36" t="n">
-        <v>822.4</v>
+        <v>814.05</v>
       </c>
       <c r="I36" t="n">
         <v>816.1610251461756</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K36" t="n">
-        <v>51.3</v>
+        <v>49.77</v>
       </c>
       <c r="L36" t="n">
         <v>7.83</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44179</v>
+        <v>44180</v>
       </c>
       <c r="H37" t="n">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="I37" t="n">
         <v>881.2890655840019</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.24</v>
+        <v>-8.84</v>
       </c>
       <c r="L37" t="n">
-        <v>8.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>2.31</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H38" t="n">
-        <v>985.8</v>
+        <v>947.5</v>
       </c>
       <c r="I38" t="n">
         <v>966.172508650486</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>11.26</v>
+        <v>6.94</v>
       </c>
       <c r="L38" t="n">
         <v>4.06</v>
@@ -2607,7 +3062,7 @@
         <v>1.35</v>
       </c>
       <c r="N38" t="n">
-        <v>3.69</v>
+        <v>3.89</v>
       </c>
       <c r="O38" t="n">
         <v>1.49</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.02</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44264</v>
+        <v>44265</v>
       </c>
       <c r="H39" t="n">
-        <v>973.15</v>
+        <v>988.5</v>
       </c>
       <c r="I39" t="n">
         <v>983.464048485665</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.71</v>
+        <v>-4.33</v>
       </c>
       <c r="L39" t="n">
         <v>5.22</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.71</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="H40" t="n">
-        <v>994.6</v>
+        <v>961.3</v>
       </c>
       <c r="I40" t="n">
         <v>963.6192490705589</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>0.62</v>
+        <v>-2.75</v>
       </c>
       <c r="L40" t="n">
         <v>5.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44354</v>
+        <v>44355</v>
       </c>
       <c r="H41" t="n">
-        <v>949.6</v>
+        <v>967.2</v>
       </c>
       <c r="I41" t="n">
         <v>958.9878191415257</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K41" t="n">
-        <v>1.22</v>
+        <v>-0.61</v>
       </c>
       <c r="L41" t="n">
         <v>4.65</v>
@@ -2778,7 +3269,7 @@
         <v>1.15</v>
       </c>
       <c r="N41" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
         <v>-3.35</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.27</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44480</v>
+        <v>44481</v>
       </c>
       <c r="H42" t="n">
-        <v>1302.9</v>
+        <v>1250.35</v>
       </c>
       <c r="I42" t="n">
         <v>1255.43915286129</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K42" t="n">
-        <v>34.71</v>
+        <v>29.28</v>
       </c>
       <c r="L42" t="n">
         <v>1.63</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44531</v>
+        <v>44532</v>
       </c>
       <c r="H43" t="n">
-        <v>1156.7</v>
+        <v>1184.7</v>
       </c>
       <c r="I43" t="n">
         <v>1183.769967288513</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K43" t="n">
-        <v>7.49</v>
+        <v>5.25</v>
       </c>
       <c r="L43" t="n">
         <v>4.69</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H44" t="n">
-        <v>1258.75</v>
+        <v>1219.75</v>
       </c>
       <c r="I44" t="n">
         <v>1252.201189986822</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K44" t="n">
-        <v>6.25</v>
+        <v>2.96</v>
       </c>
       <c r="L44" t="n">
         <v>4.5</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.96</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H45" t="n">
-        <v>1193.45</v>
+        <v>1202.85</v>
       </c>
       <c r="I45" t="n">
         <v>1201.947848843422</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K45" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="L45" t="n">
         <v>4.12</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>8.41</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H46" t="n">
-        <v>1125.1</v>
+        <v>1101.75</v>
       </c>
       <c r="I46" t="n">
         <v>1121.311176387472</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.46</v>
+        <v>-8.41</v>
       </c>
       <c r="L46" t="n">
-        <v>6.93</v>
+        <v>9.83</v>
       </c>
       <c r="M46" t="n">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="N46" t="n">
         <v>2.73</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.61</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44789</v>
+        <v>44790</v>
       </c>
       <c r="H47" t="n">
-        <v>958.2</v>
+        <v>980.6</v>
       </c>
       <c r="I47" t="n">
         <v>967.078815802354</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K47" t="n">
-        <v>13.03</v>
+        <v>11</v>
       </c>
       <c r="L47" t="n">
         <v>3.01</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.89</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H48" t="n">
-        <v>945.65</v>
+        <v>917.5</v>
       </c>
       <c r="I48" t="n">
         <v>921.4431626254648</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.56</v>
+        <v>-6.43</v>
       </c>
       <c r="L48" t="n">
-        <v>4.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.99</v>
+        <v>3.49</v>
       </c>
       <c r="N48" t="n">
-        <v>1.31</v>
+        <v>2.98</v>
       </c>
       <c r="O48" t="n">
         <v>2.34</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.61</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H49" t="n">
-        <v>946</v>
+        <v>964.55</v>
       </c>
       <c r="I49" t="n">
         <v>954.5503589569813</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.11</v>
+        <v>-5.13</v>
       </c>
       <c r="L49" t="n">
-        <v>5.01</v>
+        <v>5.5</v>
       </c>
       <c r="M49" t="n">
         <v>1.32</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.48</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H50" t="n">
-        <v>1101.35</v>
+        <v>1027.5</v>
       </c>
       <c r="I50" t="n">
         <v>1080.774652673174</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K50" t="n">
-        <v>14.18</v>
+        <v>6.53</v>
       </c>
       <c r="L50" t="n">
         <v>2.96</v>
       </c>
       <c r="M50" t="n">
-        <v>1.62</v>
+        <v>2.39</v>
       </c>
       <c r="N50" t="n">
-        <v>2.56</v>
+        <v>6.71</v>
       </c>
       <c r="O50" t="n">
         <v>1.96</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="H51" t="n">
-        <v>1077.8</v>
+        <v>1093.7</v>
       </c>
       <c r="I51" t="n">
         <v>1087.502947563018</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.9</v>
+        <v>-6.44</v>
       </c>
       <c r="L51" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="M51" t="n">
         <v>1.18</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.54</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H52" t="n">
-        <v>1083.95</v>
+        <v>1077.6</v>
       </c>
       <c r="I52" t="n">
         <v>1080.937379275133</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.89</v>
+        <v>-1.47</v>
       </c>
       <c r="L52" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="M52" t="n">
         <v>1.79</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.72</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="H53" t="n">
-        <v>1116</v>
+        <v>1139.2</v>
       </c>
       <c r="I53" t="n">
         <v>1121.103096109821</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.56</v>
+        <v>-5.72</v>
       </c>
       <c r="L53" t="n">
         <v>6.53</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.68</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45114</v>
+        <v>45117</v>
       </c>
       <c r="H54" t="n">
-        <v>1157.6</v>
+        <v>1124.5</v>
       </c>
       <c r="I54" t="n">
         <v>1141.4358221025</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K54" t="n">
-        <v>1.62</v>
+        <v>-1.29</v>
       </c>
       <c r="L54" t="n">
         <v>2.92</v>
@@ -3519,7 +4166,7 @@
         <v>0.73</v>
       </c>
       <c r="N54" t="n">
-        <v>1.95</v>
+        <v>2.86</v>
       </c>
       <c r="O54" t="n">
         <v>2.08</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.26</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="H55" t="n">
-        <v>1171</v>
+        <v>1177.15</v>
       </c>
       <c r="I55" t="n">
         <v>1175.186457216025</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.14</v>
+        <v>-4.68</v>
       </c>
       <c r="L55" t="n">
         <v>5.55</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45197</v>
+        <v>45198</v>
       </c>
       <c r="H56" t="n">
-        <v>1241.9</v>
+        <v>1234.8</v>
       </c>
       <c r="I56" t="n">
         <v>1235.814123645865</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K56" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L56" t="n">
         <v>3.22</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>5.54</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H57" t="n">
-        <v>1276.65</v>
+        <v>1311.05</v>
       </c>
       <c r="I57" t="n">
         <v>1298.305834179037</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.39</v>
+        <v>-6.18</v>
       </c>
       <c r="L57" t="n">
-        <v>4.25</v>
+        <v>6.73</v>
       </c>
       <c r="M57" t="n">
         <v>1.34</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.86</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H58" t="n">
-        <v>1595.8</v>
+        <v>1557.85</v>
       </c>
       <c r="I58" t="n">
         <v>1564.716990591179</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K58" t="n">
-        <v>21.72</v>
+        <v>18.82</v>
       </c>
       <c r="L58" t="n">
         <v>2.52</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.11</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45448</v>
+        <v>45449</v>
       </c>
       <c r="H59" t="n">
-        <v>1343.7</v>
+        <v>1397.5</v>
       </c>
       <c r="I59" t="n">
         <v>1377.034970995824</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K59" t="n">
-        <v>13.75</v>
+        <v>10.29</v>
       </c>
       <c r="L59" t="n">
         <v>2.23</v>
@@ -3804,7 +4511,7 @@
         <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>-2.38</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.44</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45670</v>
+        <v>45671</v>
       </c>
       <c r="H60" t="n">
-        <v>1989.4</v>
+        <v>1813.55</v>
       </c>
       <c r="I60" t="n">
         <v>1855.793106671624</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K60" t="n">
-        <v>42.35</v>
+        <v>29.77</v>
       </c>
       <c r="L60" t="n">
         <v>3.33</v>
       </c>
       <c r="M60" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="N60" t="n">
-        <v>3.96</v>
+        <v>8.84</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>8</v>
+      </c>
+      <c r="U60" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>13.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H61" t="n">
-        <v>1479.9</v>
+        <v>1594</v>
       </c>
       <c r="I61" t="n">
         <v>1499.731097229739</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K61" t="n">
-        <v>18.4</v>
+        <v>12.11</v>
       </c>
       <c r="L61" t="n">
         <v>6.92</v>
       </c>
       <c r="M61" t="n">
-        <v>2.12</v>
+        <v>5.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.06</v>
+        <v>7.71</v>
       </c>
       <c r="O61" t="n">
         <v>-8.84</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.2</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H62" t="n">
-        <v>1638.3</v>
+        <v>1619.8</v>
       </c>
       <c r="I62" t="n">
         <v>1630.904768244736</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K62" t="n">
-        <v>2.78</v>
+        <v>1.62</v>
       </c>
       <c r="L62" t="n">
         <v>3.57</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.21</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H63" t="n">
-        <v>1453.2</v>
+        <v>1486.5</v>
       </c>
       <c r="I63" t="n">
         <v>1465.664418139413</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K63" t="n">
-        <v>10.29</v>
+        <v>8.23</v>
       </c>
       <c r="L63" t="n">
         <v>1.4</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.52</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H64" t="n">
-        <v>1621.8</v>
+        <v>1610</v>
       </c>
       <c r="I64" t="n">
         <v>1619.448274500766</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K64" t="n">
-        <v>9.1</v>
+        <v>8.31</v>
       </c>
       <c r="L64" t="n">
         <v>2.29</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.66</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H65" t="n">
-        <v>1403.3</v>
+        <v>1441.6</v>
       </c>
       <c r="I65" t="n">
         <v>1423.481497862155</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K65" t="n">
-        <v>12.84</v>
+        <v>10.46</v>
       </c>
       <c r="L65" t="n">
         <v>1.35</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.25</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H66" t="n">
-        <v>1441.2</v>
+        <v>1285.3</v>
       </c>
       <c r="I66" t="n">
         <v>1327.297882428344</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.03</v>
+        <v>-10.84</v>
       </c>
       <c r="L66" t="n">
-        <v>3.71</v>
+        <v>11.14</v>
       </c>
       <c r="M66" t="n">
-        <v>0.88</v>
+        <v>6.67</v>
       </c>
       <c r="N66" t="n">
-        <v>1.5</v>
+        <v>10.82</v>
       </c>
       <c r="O66" t="n">
         <v>2.73</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>14.52</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H67" t="n">
-        <v>1195.1</v>
+        <v>1243.5</v>
       </c>
       <c r="I67" t="n">
         <v>1223.704083618358</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>7.02</v>
+        <v>3.25</v>
       </c>
       <c r="L67" t="n">
         <v>5.66</v>
@@ -4260,7 +5063,7 @@
         <v>1.27</v>
       </c>
       <c r="N67" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="O67" t="n">
         <v>-10.82</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>8.31</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H68" t="n">
-        <v>1146.3</v>
+        <v>1132.1</v>
       </c>
       <c r="I68" t="n">
         <v>1140.112190988059</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.82</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>8.94</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M68" t="n">
         <v>1.18</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.77</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H69" t="n">
-        <v>1134.2</v>
+        <v>1168.2</v>
       </c>
       <c r="I69" t="n">
         <v>1151.975517391736</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.19</v>
+        <v>-3.19</v>
       </c>
       <c r="L69" t="n">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="M69" t="n">
         <v>4.55</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.87</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H70" t="n">
-        <v>1277</v>
+        <v>1229.8</v>
       </c>
       <c r="I70" t="n">
         <v>1269.542128512512</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K70" t="n">
-        <v>9.31</v>
+        <v>5.27</v>
       </c>
       <c r="L70" t="n">
         <v>4.04</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>9.59</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H71" t="n">
-        <v>1223</v>
+        <v>1326</v>
       </c>
       <c r="I71" t="n">
         <v>1289.665343103516</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K71" t="n">
-        <v>0.55</v>
+        <v>-7.82</v>
       </c>
       <c r="L71" t="n">
-        <v>4.9</v>
+        <v>7.82</v>
       </c>
       <c r="M71" t="n">
         <v>3.81</v>
       </c>
       <c r="N71" t="n">
-        <v>3.95</v>
+        <v>8.42</v>
       </c>
       <c r="O71" t="n">
         <v>-3.7</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>11</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10377,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.9</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10387,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10397,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10407,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10427,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119.1</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="11">
@@ -9566,7 +10437,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -9576,7 +10447,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -9586,7 +10457,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="14">
@@ -9596,7 +10467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10477,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.81</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10487,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.05</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10497,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.3</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.4</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10517,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.96</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10527,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -9666,7 +10537,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="22">
@@ -9676,7 +10547,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10557,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="25">
@@ -9706,7 +10577,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="26">
@@ -9716,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.46</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="27">
@@ -9736,7 +10607,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
